--- a/results/extensive_linear_90p_p5_strong/original/log_extensive_verifiability_fes_normal_p90_p5_strong_b2_stage5_6_1000perm.xlsx
+++ b/results/extensive_linear_90p_p5_strong/original/log_extensive_verifiability_fes_normal_p90_p5_strong_b2_stage5_6_1000perm.xlsx
@@ -351,51 +351,147 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ver</t>
+          <t>total_reactions</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>total_comments</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>total_shares</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>n_posts</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>verifiability</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>non_ver</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fake</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>n_posts</t>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>n_posts_covid</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>pos_b_covid</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>neutral_b_covid</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>neg_b_covid</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>n_posts_vax</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>pos_b_vax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>neutral_b_vax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>neg_b_vax</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
+        <v>-0.64250684613988</v>
+      </c>
+      <c r="B2">
+        <v>-0.3416705535344707</v>
+      </c>
+      <c r="C2">
+        <v>-0.6509563015020863</v>
+      </c>
+      <c r="D2">
+        <v>-0.27884766455867</v>
+      </c>
+      <c r="E2">
+        <v>-0.256269219693689</v>
+      </c>
+      <c r="F2">
         <v>-0.1291831981914266</v>
       </c>
-      <c r="B2">
+      <c r="G2">
         <v>-0.2512806196869798</v>
       </c>
-      <c r="C2">
+      <c r="H2">
         <v>-0.08794628254796807</v>
       </c>
-      <c r="D2">
+      <c r="I2">
         <v>-0.1052861049250594</v>
       </c>
-      <c r="E2">
-        <v>-0.27884766455867</v>
+      <c r="J2">
+        <v>0.003375680043603579</v>
+      </c>
+      <c r="K2">
+        <v>-0.001399758903831926</v>
+      </c>
+      <c r="L2">
+        <v>-0.004208589276279496</v>
+      </c>
+      <c r="M2">
+        <v>0.009044828996115703</v>
+      </c>
+      <c r="N2">
+        <v>0.00428217865384002</v>
+      </c>
+      <c r="O2">
+        <v>0.0009908839851231238</v>
+      </c>
+      <c r="P2">
+        <v>0.0003340894409844219</v>
+      </c>
+      <c r="Q2">
+        <v>0.003418728219748793</v>
       </c>
     </row>
   </sheetData>
